--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:R110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>source_pdf</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>validation_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,12 +516,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>09/16/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -526,40 +531,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.324%</t>
+          <t>44.976%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.499%</t>
+          <t>16.700%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11679142</t>
+          <t>572926</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>40758</v>
+        <v>5463</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>56975298</t>
+          <t>3430693</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>57.037%</t>
+          <t>59.030%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-2.899%</t>
+          <t>4.580%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +574,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-134362303</t>
+          <t>ALSE-133925598</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +584,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134362303/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133925598/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09/16/2025</t>
+          <t>04/01/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -616,60 +626,65 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.546%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.544%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490953</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2807</v>
+        <v>1478</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12497471</t>
+          <t>3913911</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.194%</t>
+          <t>57.029%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-3.267%</t>
+          <t>-15.017%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134440891</t>
+          <t>ALSE-133929661</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134440891/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133929661/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -681,12 +696,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -701,35 +716,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.502%</t>
+          <t>8.810%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.368%</t>
+          <t>8.807%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>636278</t>
+          <t>897110</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1304</v>
+        <v>3429</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3663587</t>
+          <t>10186123</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>91.273%</t>
+          <t>48.237%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-20.270%</t>
+          <t>-15.032%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +754,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134452577</t>
+          <t>ALSE-133929692</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +764,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134452577/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133929692/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -766,55 +786,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05/26/2025</t>
+          <t>09/16/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.606%</t>
+          <t>51.375%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.602%</t>
+          <t>34.897%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33120015</t>
+          <t>139922</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>82665</v>
+        <v>676</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>385021190</t>
+          <t>400960</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>17.252%</t>
+          <t>44.414%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-2.483%</t>
+          <t>14.638%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,7 +844,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134454335</t>
+          <t>ALSE-133930227</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +854,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134454335/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133930227/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -851,80 +876,85 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>06/10/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11.527%</t>
+          <t>10.336%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.499%</t>
+          <t>10.305%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1195639</t>
+          <t>1642082</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1653</v>
+        <v>10507</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10398200</t>
+          <t>15935443</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21.588%</t>
+          <t>10.917%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.165%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134456115</t>
+          <t>ALSE-133933195</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134456115/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133933195/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -936,80 +966,85 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>05/13/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.446%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.410%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715327</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3317</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>288847628</t>
+          <t>4359093</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>28.802%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.571%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134489505</t>
+          <t>ALSE-133944728</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134489505/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133944728/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1056,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1041,60 +1076,65 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27.813%</t>
+          <t>24.663%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27.813%</t>
+          <t>2.301%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1592386</t>
+          <t>144072</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3751</v>
+        <v>4209</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5725329</t>
+          <t>6261272</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28.924%</t>
+          <t>6.702%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13.093%</t>
+          <t>0.163%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134500599</t>
+          <t>ALSE-133987625</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134500599/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133987625/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1106,80 +1146,85 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>07/01/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10.470%</t>
+          <t>10.681%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10.470%</t>
+          <t>8.079%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1508108</t>
+          <t>868409</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8856</v>
+        <v>2755</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14404088</t>
+          <t>10748969</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11.039%</t>
+          <t>13.030%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6.444%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134501724</t>
+          <t>ALSE-134024995</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134501724/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134024995/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1191,80 +1236,85 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/01/2025</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.182%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>36.182%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1394644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2917</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3854523</t>
+          <t>259775379</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>39.146%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>18.827%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134506974</t>
+          <t>ALSE-134108451</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134506974/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134108451/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1326,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>12/09/2024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1291,40 +1341,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.233%</t>
+          <t>7.309%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.195%</t>
+          <t>5.008%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>936187</t>
+          <t>257371</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5488</v>
+        <v>25044</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4036224</t>
+          <t>5139339</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>72.350%</t>
+          <t>5.987%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>6.493%</t>
+          <t>1.543%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1384,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134598852</t>
+          <t>ALSE-134198233</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1394,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134598852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134198233/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>10/28/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1381,35 +1436,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.615%</t>
+          <t>10.814%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.473%</t>
+          <t>10.811%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1191905</t>
+          <t>40159349</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>17504</v>
+        <v>94804</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34314648</t>
+          <t>371468807</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6.425%</t>
+          <t>39.017%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.683%</t>
+          <t>2.385%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1419,7 +1474,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134635543</t>
+          <t>ALSE-134212750</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1484,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134635543/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134212750/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1506,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1466,35 +1526,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>14.013%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.954%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>848778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2449</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7100190</t>
+          <t>9918560</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>44.037%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.661%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,22 +1564,27 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>ALSE-134218565</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134218565/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1596,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1551,35 +1616,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.673%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.274%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4264933</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11746</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24689228</t>
+          <t>9508195</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>51.634%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-2.432%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,22 +1654,27 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>ALSE-134218565</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134218565/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1686,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>11/11/2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1636,7 +1706,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.673%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1654,7 +1724,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9112247</t>
+          <t>3845731</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1674,22 +1744,27 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>ALSE-134218565</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134218565/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1701,55 +1776,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.000%</t>
+          <t>47.324%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.575%</t>
+          <t>20.499%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7746706</t>
+          <t>11679142</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>22451</v>
+        <v>40758</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>73251862</t>
+          <t>56975298</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52.330%</t>
+          <t>57.037%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-15.584%</t>
+          <t>-2.899%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1759,7 +1834,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>ALSE-134362303</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1769,12 +1844,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134362303/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1866,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>09/16/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1806,35 +1886,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.431%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12099296</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>47423</v>
+        <v>2807</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>188142494</t>
+          <t>12497471</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>41.520%</t>
+          <t>20.194%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-16.865%</t>
+          <t>-3.267%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1844,7 +1924,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>ALSE-134440891</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1854,12 +1934,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134440891/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1956,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1891,35 +1976,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>17.502%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.019%</t>
+          <t>17.368%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>668230</t>
+          <t>636278</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15791</v>
+        <v>1304</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>65553924</t>
+          <t>3663587</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>32.408%</t>
+          <t>91.273%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-16.925%</t>
+          <t>-20.270%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1929,7 +2014,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>ALSE-134452577</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1939,12 +2024,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134452577/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1956,12 +2046,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>05/26/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1976,60 +2066,65 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>34.091%</t>
+          <t>8.606%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.489%</t>
+          <t>8.602%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2410417</t>
+          <t>33120015</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2351</v>
+        <v>82665</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7905887</t>
+          <t>385021190</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>81.915%</t>
+          <t>17.252%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-11.679%</t>
+          <t>-2.483%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GECC-134661852</t>
+          <t>ALSE-134454335</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134454335/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2136,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2061,60 +2156,65 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>74.348%</t>
+          <t>11.527%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>56.469%</t>
+          <t>11.499%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>16269829</t>
+          <t>1195639</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>13269</v>
+        <v>1653</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28812212</t>
+          <t>10398200</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>135.921%</t>
+          <t>21.588%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-24.946%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GECC-134661852</t>
+          <t>ALSE-134456115</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134456115/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2226,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2141,65 +2241,70 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>552597</t>
+          <t>288847628</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>LBPM-134825266</t>
+          <t>ALSE-134489505</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134489505/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2211,80 +2316,85 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>27.813%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>27.813%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3151047</t>
+          <t>1592386</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10266</v>
+        <v>3751</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31426248</t>
+          <t>5725329</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>28.924%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>13.093%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>LBPM-134825266</t>
+          <t>ALSE-134500599</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134500599/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2296,80 +2406,85 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.470%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.094%</t>
+          <t>10.470%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-311663</t>
+          <t>1508108</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>212801</v>
+        <v>8856</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>331679622</t>
+          <t>14404088</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>139.114%</t>
+          <t>11.039%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-58.224%</t>
+          <t>6.444%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>PRGS-134206539</t>
+          <t>ALSE-134501724</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134501724/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2381,80 +2496,85 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>12/01/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>36.182%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.034%</t>
+          <t>36.182%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-48815</t>
+          <t>1394644</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>84134</v>
+        <v>2917</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>144277657</t>
+          <t>3854523</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>151.139%</t>
+          <t>39.146%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-54.884%</t>
+          <t>18.827%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>PRGS-134206539</t>
+          <t>ALSE-134506974</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134506974/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2466,55 +2586,55 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.078%</t>
+          <t>23.233%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.976%</t>
+          <t>23.195%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>12436677</t>
+          <t>936187</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>178171</v>
+        <v>5488</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>249949453</t>
+          <t>4036224</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20.960%</t>
+          <t>72.350%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-8.513%</t>
+          <t>6.493%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2524,7 +2644,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>PRGS-134304882</t>
+          <t>ALSE-134598852</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2534,12 +2654,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134598852/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2676,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2571,35 +2696,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.514%</t>
+          <t>9.615%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4.415%</t>
+          <t>3.473%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5696155</t>
+          <t>1191905</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>73976</v>
+        <v>17504</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>129010874</t>
+          <t>34314648</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>17.679%</t>
+          <t>6.425%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-4.703%</t>
+          <t>0.683%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2609,7 +2734,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>PRGS-134304882</t>
+          <t>ALSE-134635543</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2619,12 +2744,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134635543/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2636,12 +2766,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2651,40 +2781,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8.410%</t>
+          <t>34.591%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.865%</t>
+          <t>10.693%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23229304</t>
+          <t>7095841</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>212801</v>
+        <v>27937</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>338370673</t>
+          <t>66362571</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>15.444%</t>
+          <t>21.087%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-5.214%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2694,7 +2824,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>PRGS-134617486</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2704,12 +2834,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2856,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2736,40 +2871,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>34.591%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.003%</t>
+          <t>16.784%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-4282</t>
+          <t>43189647</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>84134</v>
+        <v>82241</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>145129258</t>
+          <t>257319717</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22.222%</t>
+          <t>34.516%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-12.417%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2779,7 +2914,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>PRGS-134617486</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2789,12 +2924,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2946,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2821,40 +2961,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>34.591%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12.637%</t>
+          <t>16.070%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1529646</t>
+          <t>15703744</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>24758</v>
+        <v>29544</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>12104575</t>
+          <t>97723183</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>35.507%</t>
+          <t>30.475%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-4.255%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2864,7 +3004,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PRGS-134618970</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2874,12 +3014,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2891,12 +3036,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2906,40 +3051,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>30.986%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11.765%</t>
+          <t>20.181%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>721225</t>
+          <t>42333354</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12489</v>
+        <v>73711</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6130291</t>
+          <t>209768324</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>35.429%</t>
+          <t>41.297%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-3.540%</t>
+          <t>3.771%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2949,7 +3094,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>PRGS-134618970</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2959,12 +3104,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -2976,12 +3126,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2991,40 +3141,40 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15.079%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>9.604%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4089402</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>11770</v>
+        <v>2596</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>42579372</t>
+          <t>6967367</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>103.005%</t>
+          <t>22.358%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-37.335%</t>
+          <t>-15.084%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3034,22 +3184,27 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>LBPM-134446500</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3061,55 +3216,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>34.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14.979%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1260251</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5203</v>
+        <v>26744</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8413197</t>
+          <t>64594518</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>90.241%</t>
+          <t>27.011%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-38.215%</t>
+          <t>-21.927%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3119,22 +3274,27 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134587304</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3306,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3166,35 +3326,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>19.515%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5.562%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2131676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>14992</v>
+        <v>12312</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>38322893</t>
+          <t>24877707</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31.358%</t>
+          <t>32.045%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-11.312%</t>
+          <t>-24.637%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3204,22 +3364,27 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>SFMA-134207336</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3396,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3251,35 +3416,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12.802%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.451%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>65333740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>471771</v>
+        <v>4480</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>773123310</t>
+          <t>9324766</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>39.658%</t>
+          <t>21.704%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-10.532%</t>
+          <t>-26.917%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3289,22 +3454,27 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>SFMA-134207336</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3486,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3331,40 +3501,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>15.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.928%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>988</v>
+        <v>71323</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>618865</t>
+          <t>211974888</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>24.824%</t>
+          <t>32.194%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-10.038%</t>
+          <t>-24.944%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3374,22 +3544,27 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>SFMA-134207352</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3416,40 +3591,40 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.935%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12302</v>
+        <v>25260</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4826799</t>
+          <t>78205161</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17.063%</t>
+          <t>31.679%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-15.535%</t>
+          <t>-16.869%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3459,22 +3634,27 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>SFMA-134207352</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3666,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Secure Insurance</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3501,40 +3681,40 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>33.352%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.953%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>60</v>
+        <v>70869</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>20336786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20.430%</t>
+          <t>40.318%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.321%</t>
+          <t>-32.351%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3544,22 +3724,27 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>SFMA-134207394</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3756,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3586,40 +3771,40 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>33.352%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>9.987%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>275821</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3997</v>
+        <v>70869</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2761789</t>
+          <t>20336786</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>24.641%</t>
+          <t>40.318%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-3.157%</t>
+          <t>-32.351%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3629,22 +3814,27 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>SFMA-134207394</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3656,12 +3846,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3671,40 +3861,40 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>44.880%</t>
+          <t>14.013%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15.049%</t>
+          <t>11.954%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>848778</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>89</v>
+        <v>2449</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7100190</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>44.037%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7.963%</t>
+          <t>-0.661%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3714,7 +3904,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>SFMA-134207400</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3724,12 +3914,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3936,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3756,40 +3951,40 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>44.880%</t>
+          <t>40.673%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10.492%</t>
+          <t>17.274%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>569929</t>
+          <t>4264933</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>23890</v>
+        <v>11746</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5432068</t>
+          <t>24689228</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50.000%</t>
+          <t>51.634%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.432%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3799,7 +3994,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>SFMA-134207400</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3809,12 +4004,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3826,12 +4026,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3846,35 +4046,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>40.673%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>9112247</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>19632</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>32973867</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>22.218%</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-29.296%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3884,7 +4084,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>SFMA-134293428</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3894,12 +4094,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3911,12 +4116,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3931,35 +4136,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>41.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.575%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7746706</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>461410</v>
+        <v>22451</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>574804392</t>
+          <t>73251862</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>31.288%</t>
+          <t>52.330%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-29.283%</t>
+          <t>-15.584%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3969,7 +4174,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>SFMA-134293428</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3979,12 +4184,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3996,55 +4206,55 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29.236%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24.908%</t>
+          <t>6.431%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1227629</t>
+          <t>12099296</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10157</v>
+        <v>47423</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4928614</t>
+          <t>188142494</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>29.493%</t>
+          <t>41.520%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>15.948%</t>
+          <t>-16.865%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4054,7 +4264,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>SFMA-134400219</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4064,12 +4274,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4081,12 +4296,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4101,35 +4316,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>21.094%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.861%</t>
+          <t>1.019%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>987176</t>
+          <t>668230</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20202</v>
+        <v>15791</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>34509460</t>
+          <t>65553924</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>387.674%</t>
+          <t>32.408%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-85.971%</t>
+          <t>-16.925%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4139,7 +4354,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>SFMA-134576755</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4149,12 +4364,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4386,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4186,60 +4406,65 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8.538%</t>
+          <t>34.091%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.694%</t>
+          <t>30.489%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>22650482</t>
+          <t>2410417</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>464314</v>
+        <v>2351</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>840691111</t>
+          <t>7905887</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>521.639%</t>
+          <t>81.915%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-93.331%</t>
+          <t>-11.679%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134576755</t>
+          <t>GECC-134661852</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4476,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4266,60 +4491,70 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>74.348%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.001%</t>
+          <t>56.469%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>16269829</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1098</v>
+        <v>13269</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>650459</t>
+          <t>28812212</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>27.169%</t>
+          <t>135.921%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-22.150%</t>
+          <t>-24.946%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>SFMA-134657574</t>
+          <t>GECC-134661852</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4331,12 +4566,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4346,35 +4581,40 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>28.915%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.035%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>12013</v>
+        <v>184</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4813803</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29.143%</t>
+          <t>9.677%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-23.280%</t>
+          <t>3.354%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4384,7 +4624,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134657574</t>
+          <t>LBPM-133813014</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4394,12 +4634,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4411,12 +4656,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4426,35 +4671,40 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>28.915%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.464%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2561016</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>93</v>
+        <v>8004</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.044%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.997%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4464,7 +4714,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>SFMA-134657690</t>
+          <t>LBPM-133813014</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4474,12 +4724,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4746,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/18/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4506,7 +4761,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4516,50 +4776,55 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>22159</v>
+        <v>184</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6226337</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.112%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.019%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134657690</t>
+          <t>LBPM-133917124</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4836,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>03/18/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4586,7 +4851,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4600,46 +4870,51 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>129</v>
+        <v>8004</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>25.385%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-14.527%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>SFMA-134657829</t>
+          <t>LBPM-133917124</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4926,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>05/20/2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4666,35 +4941,40 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.001%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3383</v>
+        <v>184</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>3157064</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>21.703%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-19.559%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4704,7 +4984,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>SFMA-134657829</t>
+          <t>LBPM-133917345</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4714,12 +4994,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4731,80 +5016,5245 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>05/20/2024</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>8004</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20547982</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>LBPM-133917345</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2023-12-15</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>8.109%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8.109%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>22376</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>97</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>275931</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>86.140%</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-26.742%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>LBPM-133959002</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-0.093%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-0.093%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-22376</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>7911</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>23950642</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>202.705%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-44.485%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>LBPM-133959002</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>07/02/2024</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>44.500%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>25.010%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>700756</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>23600</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2801932</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>29.690%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>LBPM-134070855</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>07/02/2024</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>44.500%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>26.230%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2484</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>21</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>9470</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>28.320%</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>16.410%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>LBPM-134070855</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>11.200%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>61748</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>165</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>552597</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>LBPM-134825266</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3151047</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>10266</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>31426248</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>22.500%</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>LBPM-134825266</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>05/17/2024</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>20.800%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>8.464%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>809365</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>20514</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>9562952</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>42.967%</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-7.911%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>PRGS-133796059</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>05/17/2024</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>20.800%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>7.720%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>404153</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>11559</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>5235063</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>48.534%</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-8.216%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>PRGS-133796059</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>06/14/2024</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9.657%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2.767%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5190745</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>131147</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>187628409</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>28.839%</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-14.718%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>PRGS-133908022</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>06/14/2024</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>15.044%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>4.857%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6334810</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>77006</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>130426345</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>35.330%</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-19.014%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>PRGS-133908022</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-0.094%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-311663</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>212801</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>331679622</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>139.114%</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-58.224%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>PRGS-134206539</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-0.034%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-48815</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>84134</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>144277657</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>151.139%</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-54.884%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>PRGS-134206539</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>01/24/2025</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10.078%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>4.976%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>12436677</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>178171</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>249949453</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>20.960%</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-8.513%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>PRGS-134304882</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01/24/2025</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4.514%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>4.415%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>5696155</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>73976</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>129010874</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>17.679%</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-4.703%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>PRGS-134304882</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8.410%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>6.865%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>23229304</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>212801</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>338370673</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>15.444%</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-5.214%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>PRGS-134617486</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>4.300%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-0.003%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-4282</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>84134</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>145129258</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>22.222%</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-12.417%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>PRGS-134617486</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>11/21/2025</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>12.637%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1529646</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>24758</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>12104575</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>35.507%</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-4.255%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>PRGS-134618970</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>11/21/2025</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>11.765%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>721225</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>12489</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>6130291</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>35.429%</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-3.540%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>PRGS-134618970</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>06/27/2024</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>17.600%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>15.963%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1591348</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>7054</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>9968913</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>108.729%</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-47.427%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>LBPM-134016380</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134016380/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10/02/2024</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>32.700%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>7.136%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>91374</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1570</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1280535</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>108.945%</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-13.265%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>LBPM-134016692</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134016692/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>06/21/2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>15.079%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>9.604%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>4089402</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>11770</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>42579372</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>103.005%</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-37.335%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>LBPM-134446500</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>34.200%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>14.979%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1260251</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>5203</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>8413197</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>90.241%</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-38.215%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>LBPM-134587304</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>08/15/2024</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-7.429%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-444</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>42178</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>25637633</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>21.016%</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-18.946%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SFMA-133718498</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133718498/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>02/15/2024</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>12973</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>26934045</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>23.298%</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-19.292%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SFMA-133804248</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>02/15/2024</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>457151</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>509230586</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>29.298%</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-29.626%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SFMA-133804248</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-0.037%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-877</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>3459</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2390223</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>12.982%</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-4.962%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SFMA-133834795</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2023-09-29</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133834795/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>22.500%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>6.256%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2031260</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>13731</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>32467635</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>25.093%</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-0.135%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SFMA-133866614</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>21.943%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>16.114%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>107538939</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>472743</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>667363585</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>26.465%</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-0.149%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SFMA-133866614</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0.019%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>993</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>587917</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0.081%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SFMA-133866656</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0.026%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>12453</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>4693200</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0.088%</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SFMA-133866656</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.013%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>90</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0.056%</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SFMA-133866769</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>05/06/2024</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-0.002%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-88</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>23353</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>5303794</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-0.044%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SFMA-133866769</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>03/21/2024</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>213904</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>135349235</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SFMA-133905060</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133905060/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>05/15/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>14.275%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>9.943%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>13494733</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>214157</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>135725334</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>44.648%</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-44.541%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SFMA-133937492</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133937492/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>02/13/2025</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>12.565%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0.239%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1483</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>988</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>620002</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>10.539%</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-8.078%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SFMA-134076824</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>02/13/2025</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>12.565%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0.053%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>12302</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>4752472</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>10.905%</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-9.657%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SFMA-134076824</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>19.515%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>5.562%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2131676</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>14992</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>38322893</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>31.358%</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-11.312%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SFMA-134207336</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>12.802%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>8.451%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>65333740</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>471771</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>773123310</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>39.658%</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-10.532%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SFMA-134207336</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>15.860%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>3.928%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>24307</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>988</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>618865</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>24.824%</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-10.038%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SFMA-134207352</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>15.860%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.935%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>45139</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>12302</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>4826799</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>17.063%</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-15.535%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SFMA-134207352</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>33.352%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>9.953%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>60</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>48460</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>20.430%</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-0.321%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SFMA-134207394</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>33.352%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>9.987%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>275821</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>3997</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2761789</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>24.641%</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>-3.157%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SFMA-134207394</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>44.880%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>15.049%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>89</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>25.000%</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>7.963%</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SFMA-134207400</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>44.880%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>10.492%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>569929</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>23890</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5432068</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>50.000%</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SFMA-134207400</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>19632</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>32973867</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>22.218%</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-29.296%</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>SFMA-134293428</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>461410</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>574804392</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>31.288%</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-29.283%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>SFMA-134293428</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>11/15/2025</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>29.236%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>24.908%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1227629</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>10157</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>4928614</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>29.493%</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>15.948%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SFMA-134400219</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>21.094%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2.861%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>987176</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>20202</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>34509460</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>387.674%</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-85.971%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>SFMA-134576755</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>8.538%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2.694%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>22650482</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>464314</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>840691111</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>521.639%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-93.331%</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SFMA-134576755</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-0.001%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>1098</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>650459</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>27.169%</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-22.150%</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>SFMA-134657574</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>12013</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>4813803</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>29.143%</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-23.280%</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>SFMA-134657574</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>93</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>11416</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>SFMA-134657690</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>22159</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>6226337</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0.112%</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-0.019%</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>SFMA-134657690</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>129</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>100484</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>25.385%</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-14.527%</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-0.001%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>3383</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>3157064</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>21.703%</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-19.559%</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>02/23/2024</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>27.500%</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>14.469%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>7425268</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>61714</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>51317960</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>70.800%</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-5.346%</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>TRVD-133837636</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133837636/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>02/16/2025</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1.600%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0.007%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>63226</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>62314056</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>25.324%</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-25.317%</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>TRVD-134105768</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134105768/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>09/26/2025</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Travelers Property Casualty Insurance Company</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>21.499%</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>14.416%</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>8787343</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I110" t="n">
         <v>58932</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>60957168</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>27.673%</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>-11.978%</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>TRVD-G134570380</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>output/pdfs/NV/134594460/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,6 +1107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1137,6 +1207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1227,6 +1307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1317,6 +1407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1407,6 +1507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1497,6 +1607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1587,6 +1707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1677,6 +1807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1767,6 +1907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1854,7 +2004,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1944,7 +2104,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2204,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2304,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2404,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2504,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2604,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2704,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2804,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2904,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2754,7 +3004,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2847,6 +3107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2937,6 +3207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3027,6 +3307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3117,6 +3407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3207,6 +3507,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3297,6 +3607,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3387,6 +3707,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3477,6 +3807,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3567,6 +3907,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3657,6 +4007,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3747,6 +4107,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3837,6 +4207,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3924,7 +4304,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4404,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4504,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4604,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4704,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4804,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4904,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4554,7 +5004,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4647,6 +5107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4737,6 +5207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4827,6 +5307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4917,6 +5407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5007,6 +5507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5097,6 +5607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5187,6 +5707,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5277,6 +5807,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5367,6 +5907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5457,6 +6007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5544,7 +6104,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5634,7 +6204,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5727,6 +6307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5817,6 +6407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5907,6 +6507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5997,6 +6607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6084,7 +6704,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6804,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6904,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6354,7 +7004,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6444,7 +7104,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6534,7 +7204,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6624,7 +7304,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6714,7 +7404,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6807,6 +7507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6897,6 +7607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6984,7 +7704,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7804,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7167,6 +7907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7257,6 +8007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7347,6 +8107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7432,6 +8202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7522,6 +8302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7612,6 +8402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7697,6 +8497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7782,6 +8592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7867,6 +8687,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7952,6 +8782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8037,6 +8877,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8127,6 +8977,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8217,6 +9077,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8307,6 +9177,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8394,7 +9274,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8484,7 +9374,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8574,7 +9474,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8664,7 +9574,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8754,7 +9674,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8844,7 +9774,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8934,7 +9874,17 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9974,17 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9114,7 +10074,17 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9204,7 +10174,17 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9294,7 +10274,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9384,7 +10374,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9474,7 +10474,17 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9559,7 +10569,17 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9644,7 +10664,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9729,7 +10759,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9814,7 +10854,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9899,7 +10949,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9984,7 +11044,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10077,6 +11147,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10167,6 +11247,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10254,7 +11344,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T110"/>
+  <dimension ref="A1:U110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,9 +1124,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1214,9 +1225,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1314,9 +1326,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,9 +1427,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1514,9 +1528,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1614,9 +1629,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1714,9 +1730,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1814,9 +1831,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1914,9 +1932,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2004,7 +2023,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2014,7 +2033,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2128,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2114,7 +2138,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2233,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2214,7 +2243,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2338,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2314,7 +2348,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2443,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2414,7 +2453,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2548,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2514,7 +2558,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2614,9 +2663,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2714,9 +2764,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2814,9 +2865,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2904,7 +2956,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2914,7 +2966,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3061,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3014,7 +3071,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -3114,9 +3176,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3214,9 +3277,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3314,9 +3378,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3414,9 +3479,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3504,7 +3570,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3514,9 +3580,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3604,7 +3671,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3614,9 +3681,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3704,7 +3772,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3714,9 +3782,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,7 +3873,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3814,9 +3883,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3904,7 +3974,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -3914,9 +3984,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4004,7 +4075,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4014,9 +4085,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4104,7 +4176,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4114,9 +4186,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4204,7 +4277,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4214,9 +4287,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4304,7 +4378,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4314,7 +4388,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4483,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4414,7 +4493,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4588,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4514,7 +4598,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -4614,9 +4703,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4714,9 +4804,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4814,9 +4905,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4914,9 +5006,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5014,9 +5107,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5114,9 +5208,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5214,9 +5309,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5314,9 +5410,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5414,9 +5511,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5514,9 +5612,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5614,9 +5713,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5704,7 +5804,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5714,7 +5814,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5909,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -5814,7 +5919,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5914,9 +6024,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6014,9 +6125,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6114,9 +6226,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6214,9 +6327,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6314,9 +6428,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6414,9 +6529,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6514,9 +6630,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6614,9 +6731,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6714,9 +6832,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6814,9 +6933,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6904,7 +7024,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -6914,7 +7034,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -7004,7 +7129,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7014,7 +7139,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7234,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7114,7 +7244,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7339,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7214,7 +7349,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7444,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7314,7 +7454,12 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7549,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7414,7 +7559,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -7514,9 +7664,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7614,9 +7765,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7704,7 +7856,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -7714,7 +7866,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7961,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -7814,7 +7971,12 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -7914,9 +8076,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8014,9 +8177,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8114,9 +8278,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8209,9 +8374,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8309,9 +8475,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8409,9 +8576,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8504,9 +8672,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8599,9 +8768,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8694,9 +8864,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8789,9 +8960,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8884,9 +9056,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8974,7 +9147,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -8984,7 +9157,12 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9252,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9084,7 +9262,12 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9357,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9184,7 +9367,12 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9462,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9284,7 +9472,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9567,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -9384,7 +9577,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9672,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9484,7 +9682,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9777,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9584,7 +9787,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9882,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -9684,7 +9892,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>reclassified</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9987,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9784,7 +9997,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>reclassified</t>
         </is>
       </c>
     </row>
@@ -9874,7 +10092,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -9884,7 +10102,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>reclassified</t>
         </is>
       </c>
     </row>
@@ -9974,7 +10197,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -9984,7 +10207,12 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>reclassified</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10302,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10084,7 +10312,12 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10407,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10184,7 +10417,12 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10512,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10284,7 +10522,12 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10617,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10384,7 +10627,12 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10722,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10484,7 +10732,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10579,9 +10832,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10674,9 +10928,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10769,9 +11024,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10864,9 +11120,10 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10959,9 +11216,10 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11054,9 +11312,10 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11154,9 +11413,10 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11244,7 +11504,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11254,7 +11514,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11609,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11354,7 +11619,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -10822,7 +10822,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -10832,10 +10832,14 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10918,7 +10922,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -10928,10 +10932,14 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -11014,7 +11022,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11024,10 +11032,14 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>reclassified</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11206,7 +11218,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11216,10 +11228,14 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>reclassified</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11302,7 +11318,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11312,10 +11328,14 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>reclassified</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2033,14 +2033,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2128,7 +2124,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2138,14 +2134,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2233,7 +2225,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2243,14 +2235,10 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2338,7 +2326,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2348,14 +2336,10 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2443,7 +2427,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2453,14 +2437,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2548,7 +2528,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2558,14 +2538,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2956,7 +2932,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2966,14 +2942,10 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3061,7 +3033,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3071,14 +3043,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3088,80 +3056,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02/03/2024</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>34.591%</t>
+          <t>17.280%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10.693%</t>
+          <t>8.596%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7095841</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>27937</v>
+        <v>549</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>66362571</t>
+          <t>452342</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21.087%</t>
+          <t>36.937%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.316%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GECC-133800350</t>
+          <t>ALSE-134847042</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134847042/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3171,12 +3139,12 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
@@ -3189,55 +3157,55 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>02/03/2024</t>
+          <t>06/17/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>34.591%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.784%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>43189647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>82241</v>
+        <v>12341</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>257319717</t>
+          <t>1959967</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>34.516%</t>
+          <t>1.907%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.081%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3247,7 +3215,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GECC-133800350</t>
+          <t>ALSE-134850653</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3257,12 +3225,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134850653/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3272,12 +3240,12 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
@@ -3290,12 +3258,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02/03/2024</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3305,35 +3273,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>34.591%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>16.070%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15703744</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>29544</v>
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>97723183</t>
+          <t>237196102</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30.475%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3343,27 +3311,27 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GECC-133800350</t>
+          <t>ALSE-134916248</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134916248/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3373,12 +3341,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -3396,7 +3364,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3411,35 +3379,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>30.986%</t>
+          <t>34.591%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.181%</t>
+          <t>10.693%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>42333354</t>
+          <t>7095841</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>73711</v>
+        <v>27937</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>209768324</t>
+          <t>66362571</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>41.297%</t>
+          <t>21.087%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3.771%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3492,12 +3460,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3507,42 +3475,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>34.591%</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>16.784%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>43189647</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>82241</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>257319717</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>34.516%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>2596</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>6967367</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>22.358%</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>-15.084%</t>
-        </is>
-      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -3550,22 +3518,22 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>GECC-134012732</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Approved with Stipulations</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3580,7 +3548,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -3593,12 +3561,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3608,42 +3576,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>34.591%</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>16.070%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>15703744</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>29544</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>97723183</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>30.475%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>0.000%</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>26744</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>64594518</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>27.011%</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>-21.927%</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -3651,22 +3619,22 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>GECC-134012732</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Approved with Stipulations</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3681,7 +3649,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
@@ -3694,12 +3662,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>02/03/2024</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3709,40 +3677,40 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>30.986%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.181%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42333354</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>12312</v>
+        <v>73711</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24877707</t>
+          <t>209768324</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>32.045%</t>
+          <t>41.297%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-24.637%</t>
+          <t>3.771%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3752,22 +3720,22 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GECC-134012732</t>
+          <t>GECC-133800350</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Approved with Stipulations</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133800350/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3782,7 +3750,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
@@ -3800,7 +3768,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3829,21 +3797,21 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4480</v>
+        <v>2596</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9324766</t>
+          <t>6967367</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21.704%</t>
+          <t>22.358%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-26.917%</t>
+          <t>-15.084%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3901,7 +3869,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3930,21 +3898,21 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>71323</v>
+        <v>26744</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>211974888</t>
+          <t>64594518</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>32.194%</t>
+          <t>27.011%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-24.944%</t>
+          <t>-21.927%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4002,7 +3970,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4031,21 +3999,21 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>25260</v>
+        <v>12312</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78205161</t>
+          <t>24877707</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>31.679%</t>
+          <t>32.045%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-16.869%</t>
+          <t>-24.637%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4103,7 +4071,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4132,21 +4100,21 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>70869</v>
+        <v>4480</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20336786</t>
+          <t>9324766</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>40.318%</t>
+          <t>21.704%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-32.351%</t>
+          <t>-26.917%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4204,7 +4172,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4233,21 +4201,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>70869</v>
+        <v>71323</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>20336786</t>
+          <t>211974888</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>40.318%</t>
+          <t>32.194%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-32.351%</t>
+          <t>-24.944%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4300,12 +4268,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4320,35 +4288,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14.013%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>11.954%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>848778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2449</v>
+        <v>25260</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7100190</t>
+          <t>78205161</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>44.037%</t>
+          <t>31.679%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.661%</t>
+          <t>-16.869%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4358,44 +4326,40 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4405,12 +4369,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Secure Insurance</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4425,35 +4389,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>40.673%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>17.274%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4264933</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>11746</v>
+        <v>70869</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>24689228</t>
+          <t>20336786</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>51.634%</t>
+          <t>40.318%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-2.432%</t>
+          <t>-32.351%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4463,44 +4427,40 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4510,12 +4470,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4530,7 +4490,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>40.673%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4544,21 +4504,21 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>70869</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>9112247</t>
+          <t>20336786</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>40.318%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-32.351%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4568,44 +4528,40 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>GECC-134012732</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Approved with Stipulations</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-03-15</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4615,12 +4571,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4635,35 +4591,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>41.000%</t>
+          <t>14.013%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10.575%</t>
+          <t>11.954%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>7746706</t>
+          <t>848778</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>22451</v>
+        <v>2449</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>73251862</t>
+          <t>7100190</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>52.330%</t>
+          <t>44.037%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-15.584%</t>
+          <t>-0.661%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4673,7 +4629,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4683,12 +4639,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4716,12 +4672,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4736,35 +4692,35 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>40.673%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.431%</t>
+          <t>17.274%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12099296</t>
+          <t>4264933</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>47423</v>
+        <v>11746</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>188142494</t>
+          <t>24689228</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>41.520%</t>
+          <t>51.634%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-16.865%</t>
+          <t>-2.432%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4774,7 +4730,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4784,12 +4740,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4817,12 +4773,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4837,35 +4793,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>40.673%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1.019%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>668230</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>15791</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>65553924</t>
+          <t>9112247</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>32.408%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-16.925%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4875,7 +4831,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4885,12 +4841,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4923,7 +4879,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4938,60 +4894,60 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>34.091%</t>
+          <t>41.000%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>30.489%</t>
+          <t>10.575%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2410417</t>
+          <t>7746706</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2351</v>
+        <v>22451</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>7905887</t>
+          <t>73251862</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>81.915%</t>
+          <t>52.330%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-11.679%</t>
+          <t>-15.584%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GECC-134661852</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5024,7 +4980,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5039,60 +4995,60 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>74.348%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>56.469%</t>
+          <t>6.431%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>16269829</t>
+          <t>12099296</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>13269</v>
+        <v>47423</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>28812212</t>
+          <t>188142494</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>135.921%</t>
+          <t>41.520%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-24.946%</t>
+          <t>-16.865%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GECC-134661852</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5120,12 +5076,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>04/11/2024</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5135,40 +5091,40 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>28.915%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>6.035%</t>
+          <t>1.019%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>668230</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>184</v>
+        <v>15791</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>65553924</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>9.677%</t>
+          <t>32.408%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3.354%</t>
+          <t>-16.925%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5178,7 +5134,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>LBPM-133813014</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5188,12 +5144,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5203,12 +5159,12 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -5221,12 +5177,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/11/2024</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5236,65 +5192,65 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28.915%</t>
+          <t>34.091%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12.464%</t>
+          <t>30.489%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2561016</t>
+          <t>2410417</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>8004</v>
+        <v>2351</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>7905887</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22.044%</t>
+          <t>81.915%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.997%</t>
+          <t>-11.679%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LBPM-133813014</t>
+          <t>GECC-134661852</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5304,12 +5260,12 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
@@ -5322,12 +5278,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03/18/2024</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5337,65 +5293,65 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>74.348%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>56.469%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16269829</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>184</v>
+        <v>13269</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>28812212</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>135.921%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.946%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LBPM-133917124</t>
+          <t>GECC-134661852</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5405,12 +5361,12 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -5423,12 +5379,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>03/18/2024</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5443,60 +5399,60 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>28.915%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.035%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8004</v>
+        <v>184</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.677%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.354%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-133917124</t>
+          <t>LBPM-133813014</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5524,12 +5480,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>05/20/2024</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5544,35 +5500,35 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>28.915%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.464%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2561016</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>184</v>
+        <v>8004</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.044%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.997%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5582,7 +5538,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>LBPM-133917345</t>
+          <t>LBPM-133813014</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5592,12 +5548,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5625,12 +5581,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>05/20/2024</t>
+          <t>03/18/2024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5659,11 +5615,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8004</v>
+        <v>184</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5678,27 +5634,27 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>LBPM-133917345</t>
+          <t>LBPM-133917124</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5726,12 +5682,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>03/18/2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5746,65 +5702,65 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>8.109%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8.109%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>97</v>
+        <v>8004</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>275931</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>86.140%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-26.742%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LBPM-133959002</t>
+          <t>LBPM-133917124</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5814,14 +5770,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5831,12 +5783,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>05/20/2024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5851,35 +5803,35 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-0.093%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-0.093%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-22376</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7911</v>
+        <v>184</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23950642</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>202.705%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-44.485%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5889,7 +5841,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>LBPM-133959002</t>
+          <t>LBPM-133917345</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5899,17 +5851,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -5919,14 +5871,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5936,50 +5884,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07/02/2024</t>
+          <t>05/20/2024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>44.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>700756</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>23600</v>
+        <v>8004</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2801932</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>29.690%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5994,7 +5942,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LBPM-134070855</t>
+          <t>LBPM-133917345</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -6004,12 +5952,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -6037,55 +5985,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>07/02/2024</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>44.500%</t>
+          <t>8.109%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>26.230%</t>
+          <t>8.109%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>275931</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28.320%</t>
+          <t>86.140%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>16.410%</t>
+          <t>-26.742%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6095,7 +6043,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>LBPM-134070855</t>
+          <t>LBPM-133959002</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -6105,12 +6053,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6125,7 +6073,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
@@ -6138,12 +6086,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -6158,60 +6106,60 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>-0.093%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>-0.093%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>-22376</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>165</v>
+        <v>7911</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>552597</t>
+          <t>23950642</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>202.705%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-44.485%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>LBPM-134825266</t>
+          <t>LBPM-133959002</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6221,7 +6169,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -6239,80 +6187,80 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>07/02/2024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>44.500%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>25.010%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3151047</t>
+          <t>700756</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10266</v>
+        <v>23600</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>31426248</t>
+          <t>2801932</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>29.690%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>LBPM-134825266</t>
+          <t>LBPM-134070855</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6322,12 +6270,12 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -6340,55 +6288,55 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>05/17/2024</t>
+          <t>07/02/2024</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>20.800%</t>
+          <t>44.500%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.464%</t>
+          <t>26.230%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>809365</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>20514</v>
+        <v>21</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9562952</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>42.967%</t>
+          <t>28.320%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-7.911%</t>
+          <t>16.410%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6398,7 +6346,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PRGS-133796059</t>
+          <t>LBPM-134070855</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6408,12 +6356,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6441,55 +6389,55 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>05/17/2024</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>20.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7.720%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>404153</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11559</v>
+        <v>140</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>5235063</t>
+          <t>290107</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>48.534%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-8.216%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6499,7 +6447,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-133796059</t>
+          <t>LBPM-134721941</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6509,12 +6457,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134721941/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6524,12 +6472,12 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U60" t="inlineStr"/>
@@ -6542,12 +6490,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>06/14/2024</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6557,65 +6505,65 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>9.657%</t>
+          <t>21.800%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.767%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5190745</t>
+          <t>61748</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>131147</v>
+        <v>165</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>187628409</t>
+          <t>552597</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>28.839%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-14.718%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-133908022</t>
+          <t>LBPM-134825266</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6625,12 +6573,12 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -6643,12 +6591,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>06/14/2024</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6658,65 +6606,65 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>15.044%</t>
+          <t>21.800%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.857%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6334810</t>
+          <t>3151047</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>77006</v>
+        <v>10266</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>130426345</t>
+          <t>31426248</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>35.330%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-19.014%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-133908022</t>
+          <t>LBPM-134825266</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6726,12 +6674,12 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -6744,7 +6692,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>05/17/2024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6759,65 +6707,65 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.800%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-0.094%</t>
+          <t>8.464%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-311663</t>
+          <t>809365</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>212801</v>
+        <v>20514</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>331679622</t>
+          <t>9562952</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>139.114%</t>
+          <t>42.967%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-58.224%</t>
+          <t>-7.911%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PRGS-134206539</t>
+          <t>PRGS-133796059</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6827,12 +6775,12 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -6845,7 +6793,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>05/17/2024</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6860,65 +6808,65 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.800%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-0.034%</t>
+          <t>7.720%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-48815</t>
+          <t>404153</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>84134</v>
+        <v>11559</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>144277657</t>
+          <t>5235063</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>151.139%</t>
+          <t>48.534%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-54.884%</t>
+          <t>-8.216%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>PRGS-134206539</t>
+          <t>PRGS-133796059</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6928,12 +6876,12 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
@@ -6946,7 +6894,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>06/14/2024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6966,35 +6914,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.078%</t>
+          <t>9.657%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4.976%</t>
+          <t>2.767%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>12436677</t>
+          <t>5190745</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>178171</v>
+        <v>131147</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>249949453</t>
+          <t>187628409</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20.960%</t>
+          <t>28.839%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-8.513%</t>
+          <t>-14.718%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7004,7 +6952,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>PRGS-134304882</t>
+          <t>PRGS-133908022</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -7014,34 +6962,30 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7051,7 +6995,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>06/14/2024</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -7071,35 +7015,35 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4.514%</t>
+          <t>15.044%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.415%</t>
+          <t>4.857%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5696155</t>
+          <t>6334810</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>73976</v>
+        <v>77006</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>129010874</t>
+          <t>130426345</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17.679%</t>
+          <t>35.330%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-4.703%</t>
+          <t>-19.014%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7109,7 +7053,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>PRGS-134304882</t>
+          <t>PRGS-133908022</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -7119,34 +7063,30 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7156,7 +7096,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7176,17 +7116,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>8.410%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>6.865%</t>
+          <t>-0.094%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>23229304</t>
+          <t>-311663</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -7194,47 +7134,47 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>338370673</t>
+          <t>331679622</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>15.444%</t>
+          <t>139.114%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-5.214%</t>
+          <t>-58.224%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>PRGS-134617486</t>
+          <t>PRGS-134206539</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7244,14 +7184,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7261,7 +7197,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7281,17 +7217,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-0.003%</t>
+          <t>-0.034%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-4282</t>
+          <t>-48815</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -7299,47 +7235,47 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>145129258</t>
+          <t>144277657</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>22.222%</t>
+          <t>151.139%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-12.417%</t>
+          <t>-54.884%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PRGS-134617486</t>
+          <t>PRGS-134206539</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7349,14 +7285,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7366,7 +7298,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>01/24/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7381,40 +7313,40 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>10.078%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>12.637%</t>
+          <t>4.976%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1529646</t>
+          <t>12436677</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>24758</v>
+        <v>178171</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>12104575</t>
+          <t>249949453</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>35.507%</t>
+          <t>20.960%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-4.255%</t>
+          <t>-8.513%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7424,7 +7356,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PRGS-134618970</t>
+          <t>PRGS-134304882</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7434,17 +7366,17 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7454,14 +7386,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7471,7 +7399,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>01/24/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7486,40 +7414,40 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>4.514%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>11.765%</t>
+          <t>4.415%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>721225</t>
+          <t>5696155</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12489</v>
+        <v>73976</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6130291</t>
+          <t>129010874</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>35.429%</t>
+          <t>17.679%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-3.540%</t>
+          <t>-4.703%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7529,7 +7457,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>PRGS-134618970</t>
+          <t>PRGS-134304882</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7539,17 +7467,17 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7559,14 +7487,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7576,80 +7500,80 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>06/27/2024</t>
+          <t>10/03/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17.600%</t>
+          <t>8.410%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15.963%</t>
+          <t>6.865%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1591348</t>
+          <t>23229304</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7054</v>
+        <v>212801</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>9968913</t>
+          <t>338370673</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>108.729%</t>
+          <t>15.444%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-47.427%</t>
+          <t>-5.214%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134016380</t>
+          <t>PRGS-134617486</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134016380/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7659,12 +7583,12 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
@@ -7677,55 +7601,55 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/02/2024</t>
+          <t>10/03/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>32.700%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>7.136%</t>
+          <t>-0.003%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>91374</t>
+          <t>-4282</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1570</v>
+        <v>84134</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1280535</t>
+          <t>145129258</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>108.945%</t>
+          <t>22.222%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-13.265%</t>
+          <t>-12.417%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7735,7 +7659,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>LBPM-134016692</t>
+          <t>PRGS-134617486</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7745,12 +7669,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134016692/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7760,12 +7684,12 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U72" t="inlineStr"/>
@@ -7778,12 +7702,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7793,40 +7717,40 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>15.079%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>9.604%</t>
+          <t>12.637%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4089402</t>
+          <t>1529646</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11770</v>
+        <v>24758</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>42579372</t>
+          <t>12104575</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>103.005%</t>
+          <t>35.507%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-37.335%</t>
+          <t>-4.255%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7836,7 +7760,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134446500</t>
+          <t>PRGS-134618970</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7846,17 +7770,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -7866,14 +7790,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7883,55 +7803,55 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>34.200%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14.979%</t>
+          <t>11.765%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1260251</t>
+          <t>721225</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5203</v>
+        <v>12489</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8413197</t>
+          <t>6130291</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>90.241%</t>
+          <t>35.429%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-38.215%</t>
+          <t>-3.540%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7941,7 +7861,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134587304</t>
+          <t>PRGS-134618970</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7951,17 +7871,17 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -7971,14 +7891,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7988,12 +7904,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>08/15/2024</t>
+          <t>06/27/2024</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -8003,65 +7919,65 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-7.429%</t>
+          <t>17.600%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-0.002%</t>
+          <t>15.963%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-444</t>
+          <t>1591348</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>42178</v>
+        <v>7054</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>25637633</t>
+          <t>9968913</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>21.016%</t>
+          <t>108.729%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-18.946%</t>
+          <t>-47.427%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>SFMA-133718498</t>
+          <t>LBPM-134016380</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133718498/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134016380/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -8089,55 +8005,55 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>02/15/2024</t>
+          <t>10/02/2024</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>32.700%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.136%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>12973</v>
+        <v>1570</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>26934045</t>
+          <t>1280535</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>23.298%</t>
+          <t>108.945%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-19.292%</t>
+          <t>-13.265%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8147,7 +8063,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-133804248</t>
+          <t>LBPM-134016692</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -8157,12 +8073,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134016692/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8190,12 +8106,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>02/15/2024</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -8205,40 +8121,40 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.079%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.604%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4089402</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>457151</v>
+        <v>11770</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>509230586</t>
+          <t>42579372</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>29.298%</t>
+          <t>103.005%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-29.626%</t>
+          <t>-37.335%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8248,7 +8164,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-133804248</t>
+          <t>LBPM-134446500</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8258,12 +8174,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8273,12 +8189,12 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
@@ -8291,12 +8207,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8306,35 +8222,40 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>34.200%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-0.037%</t>
+          <t>14.979%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-877</t>
+          <t>1260251</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3459</v>
+        <v>5203</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2390223</t>
+          <t>8413197</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>12.982%</t>
+          <t>90.241%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-4.962%</t>
+          <t>-38.215%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8344,7 +8265,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-133834795</t>
+          <t>LBPM-134587304</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -8354,12 +8275,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133834795/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8369,12 +8290,12 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U78" t="inlineStr"/>
@@ -8387,12 +8308,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8402,65 +8323,65 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>12.700%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6.256%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2031260</t>
+          <t>2088534</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13731</v>
+        <v>8943</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>32467635</t>
+          <t>34815867</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>25.093%</t>
+          <t>15.389%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-0.135%</t>
+          <t>-3.608%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-133866614</t>
+          <t>LBPM-134798717</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134798717/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8470,12 +8391,12 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -8488,55 +8409,55 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>08/15/2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>21.943%</t>
+          <t>-7.429%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>16.114%</t>
+          <t>-0.002%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>107538939</t>
+          <t>-444</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>472743</v>
+        <v>42178</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>667363585</t>
+          <t>25637633</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>26.465%</t>
+          <t>21.016%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-0.149%</t>
+          <t>-18.946%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8546,7 +8467,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-133866614</t>
+          <t>SFMA-133718498</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8556,12 +8477,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133718498/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8589,7 +8510,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>02/15/2024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8604,35 +8525,40 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>0.019%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>993</v>
+        <v>12973</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>587917</t>
+          <t>26934045</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.081%</t>
+          <t>23.298%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-19.292%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8642,7 +8568,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-133866656</t>
+          <t>SFMA-133804248</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8652,12 +8578,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -8685,7 +8611,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>02/15/2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8700,35 +8626,40 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.026%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>12453</v>
+        <v>457151</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4693200</t>
+          <t>509230586</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0.088%</t>
+          <t>29.298%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-29.626%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8738,7 +8669,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>SFMA-133866656</t>
+          <t>SFMA-133804248</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8748,12 +8679,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8781,7 +8712,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8791,40 +8722,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.013%</t>
+          <t>-0.037%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-877</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>90</v>
+        <v>3459</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>2390223</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0.056%</t>
+          <t>12.982%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.962%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8834,7 +8765,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-133866769</t>
+          <t>SFMA-133834795</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8844,12 +8775,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133834795/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8882,7 +8813,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8892,35 +8823,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-0.002%</t>
+          <t>6.256%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-88</t>
+          <t>2031260</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>23353</v>
+        <v>13731</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>5303794</t>
+          <t>32467635</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.093%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-0.044%</t>
+          <t>-0.135%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8930,7 +8866,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SFMA-133866769</t>
+          <t>SFMA-133866614</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8945,7 +8881,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8973,50 +8909,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>03/21/2024</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>21.943%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.114%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107538939</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>213904</v>
+        <v>472743</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>135349235</t>
+          <t>667363585</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>26.465%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.149%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9026,7 +8967,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-133905060</t>
+          <t>SFMA-133866614</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -9036,12 +8977,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133905060/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -9069,7 +9010,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9079,45 +9020,40 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>14.275%</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>9.943%</t>
+          <t>0.019%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>13494733</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>214157</v>
+        <v>993</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>135725334</t>
+          <t>587917</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>44.648%</t>
+          <t>0.081%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-44.541%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9127,7 +9063,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>SFMA-133937492</t>
+          <t>SFMA-133866656</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9137,17 +9073,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133937492/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9157,14 +9093,10 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9174,12 +9106,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>02/13/2025</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9192,37 +9124,32 @@
           <t>19.0002 Motorcycle</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>12.565%</t>
-        </is>
-      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.239%</t>
+          <t>0.026%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>988</v>
+        <v>12453</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>620002</t>
+          <t>4693200</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>10.539%</t>
+          <t>0.088%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-8.078%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9232,7 +9159,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>SFMA-134076824</t>
+          <t>SFMA-133866656</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -9242,17 +9169,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9262,14 +9189,10 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9279,12 +9202,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/13/2025</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9294,40 +9217,35 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>12.565%</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.053%</t>
+          <t>0.013%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>12302</v>
+        <v>90</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4752472</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>10.905%</t>
+          <t>0.056%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-9.657%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9337,7 +9255,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>SFMA-134076824</t>
+          <t>SFMA-133866769</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -9347,17 +9265,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9367,14 +9285,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9384,12 +9298,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9399,40 +9313,35 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>19.515%</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>5.562%</t>
+          <t>-0.002%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2131676</t>
+          <t>-88</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>14992</v>
+        <v>23353</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>38322893</t>
+          <t>5303794</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>31.358%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-11.312%</t>
+          <t>-0.044%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9442,7 +9351,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>SFMA-134207336</t>
+          <t>SFMA-133866769</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9452,34 +9361,30 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9489,55 +9394,50 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>03/21/2024</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>12.802%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>8.451%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>65333740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>471771</v>
+        <v>213904</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>773123310</t>
+          <t>135349235</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>39.658%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-10.532%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9547,7 +9447,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>SFMA-134207336</t>
+          <t>SFMA-133905060</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -9557,34 +9457,30 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133905060/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9594,7 +9490,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9604,45 +9500,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>15.860%</t>
+          <t>14.275%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>3.928%</t>
+          <t>9.943%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>13494733</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>988</v>
+        <v>214157</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>618865</t>
+          <t>135725334</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>24.824%</t>
+          <t>44.648%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-10.038%</t>
+          <t>-44.541%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9652,7 +9548,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>SFMA-134207352</t>
+          <t>SFMA-133937492</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9662,34 +9558,30 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133937492/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9699,12 +9591,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>02/13/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9719,35 +9611,35 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>15.860%</t>
+          <t>12.565%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.935%</t>
+          <t>0.239%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12302</v>
+        <v>988</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4826799</t>
+          <t>620002</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>17.063%</t>
+          <t>10.539%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-15.535%</t>
+          <t>-8.078%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9757,7 +9649,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>SFMA-134207352</t>
+          <t>SFMA-134076824</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9767,34 +9659,30 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9804,12 +9692,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>02/13/2025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9819,40 +9707,40 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>33.352%</t>
+          <t>12.565%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>9.953%</t>
+          <t>0.053%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>60</v>
+        <v>12302</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>4752472</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>20.430%</t>
+          <t>10.905%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-0.321%</t>
+          <t>-9.657%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9862,7 +9750,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>SFMA-134207394</t>
+          <t>SFMA-134076824</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9872,34 +9760,30 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9914,7 +9798,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9924,40 +9808,40 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>33.352%</t>
+          <t>19.515%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>9.987%</t>
+          <t>5.562%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>275821</t>
+          <t>2131676</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3997</v>
+        <v>14992</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2761789</t>
+          <t>38322893</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>24.641%</t>
+          <t>31.358%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-3.157%</t>
+          <t>-11.312%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9967,7 +9851,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>SFMA-134207394</t>
+          <t>SFMA-134207336</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9982,12 +9866,12 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9997,14 +9881,10 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10019,7 +9899,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -10029,40 +9909,40 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>44.880%</t>
+          <t>12.802%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>15.049%</t>
+          <t>8.451%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>65333740</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>89</v>
+        <v>471771</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>773123310</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>39.658%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>7.963%</t>
+          <t>-10.532%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10072,7 +9952,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>SFMA-134207400</t>
+          <t>SFMA-134207336</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -10087,12 +9967,12 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10102,14 +9982,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10124,7 +10000,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10134,40 +10010,40 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>44.880%</t>
+          <t>15.860%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>10.492%</t>
+          <t>3.928%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>569929</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>23890</v>
+        <v>988</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>5432068</t>
+          <t>618865</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>50.000%</t>
+          <t>24.824%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.038%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10177,7 +10053,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>SFMA-134207400</t>
+          <t>SFMA-134207352</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -10192,12 +10068,12 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10207,14 +10083,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10224,12 +10096,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10239,40 +10111,40 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.860%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.935%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>19632</v>
+        <v>12302</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>32973867</t>
+          <t>4826799</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>22.218%</t>
+          <t>17.063%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-29.296%</t>
+          <t>-15.535%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10282,7 +10154,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>SFMA-134293428</t>
+          <t>SFMA-134207352</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -10292,17 +10164,17 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10312,14 +10184,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10329,12 +10197,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10344,40 +10212,40 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>33.352%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.953%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>461410</v>
+        <v>60</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>574804392</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>31.288%</t>
+          <t>20.430%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-29.283%</t>
+          <t>-0.321%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10387,7 +10255,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>SFMA-134293428</t>
+          <t>SFMA-134207394</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -10397,17 +10265,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10417,14 +10285,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>date_relaxed</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10434,55 +10298,55 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>29.236%</t>
+          <t>33.352%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>24.908%</t>
+          <t>9.987%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1227629</t>
+          <t>275821</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>10157</v>
+        <v>3997</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4928614</t>
+          <t>2761789</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>29.493%</t>
+          <t>24.641%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>15.948%</t>
+          <t>-3.157%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10492,7 +10356,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>SFMA-134400219</t>
+          <t>SFMA-134207394</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10502,17 +10366,17 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10522,14 +10386,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10539,7 +10399,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10554,40 +10414,40 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>21.094%</t>
+          <t>44.880%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2.861%</t>
+          <t>15.049%</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>987176</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>20202</v>
+        <v>89</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>34509460</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>387.674%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-85.971%</t>
+          <t>7.963%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10597,7 +10457,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>SFMA-134576755</t>
+          <t>SFMA-134207400</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -10607,17 +10467,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10627,14 +10487,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10644,7 +10500,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10659,40 +10515,40 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>8.538%</t>
+          <t>44.880%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2.694%</t>
+          <t>10.492%</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>22650482</t>
+          <t>569929</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>464314</v>
+        <v>23890</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>840691111</t>
+          <t>5432068</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>521.639%</t>
+          <t>50.000%</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-93.331%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10702,7 +10558,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>SFMA-134576755</t>
+          <t>SFMA-134207400</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10712,17 +10568,17 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10732,14 +10588,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10749,7 +10601,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -10764,35 +10616,40 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-0.001%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1098</v>
+        <v>19632</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>650459</t>
+          <t>32973867</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>27.169%</t>
+          <t>22.218%</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>-22.150%</t>
+          <t>-29.296%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10802,7 +10659,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>SFMA-134657574</t>
+          <t>SFMA-134293428</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -10812,17 +10669,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -10832,14 +10689,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10849,7 +10702,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -10864,7 +10717,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10874,25 +10732,25 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12013</v>
+        <v>461410</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4813803</t>
+          <t>574804392</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>29.143%</t>
+          <t>31.288%</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>-23.280%</t>
+          <t>-29.283%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10902,7 +10760,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>SFMA-134657574</t>
+          <t>SFMA-134293428</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -10912,17 +10770,17 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -10932,14 +10790,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10949,7 +10803,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10959,40 +10813,45 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>29.236%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.908%</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1227629</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>93</v>
+        <v>10157</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>4928614</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>29.493%</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.948%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11002,7 +10861,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>SFMA-134657690</t>
+          <t>SFMA-134400219</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -11012,17 +10871,17 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11032,14 +10891,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11054,7 +10909,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -11064,35 +10919,40 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>21.094%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.861%</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>987176</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>22159</v>
+        <v>20202</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6226337</t>
+          <t>34509460</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>0.112%</t>
+          <t>387.674%</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>-0.019%</t>
+          <t>-85.971%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11102,7 +10962,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>SFMA-134657690</t>
+          <t>SFMA-134576755</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -11112,12 +10972,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -11150,7 +11010,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11160,35 +11020,40 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>8.538%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.694%</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22650482</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>129</v>
+        <v>464314</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>840691111</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>25.385%</t>
+          <t>521.639%</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>-14.527%</t>
+          <t>-93.331%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11198,7 +11063,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>SFMA-134657829</t>
+          <t>SFMA-134576755</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -11208,17 +11073,17 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11228,14 +11093,10 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11250,7 +11111,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11260,7 +11121,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -11270,25 +11131,25 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3383</v>
+        <v>1098</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>3157064</t>
+          <t>650459</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>21.703%</t>
+          <t>27.169%</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>-19.559%</t>
+          <t>-22.150%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11298,7 +11159,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>SFMA-134657829</t>
+          <t>SFMA-134657574</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -11313,12 +11174,12 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11328,14 +11189,10 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>reclassified</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11345,55 +11202,50 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>02/23/2024</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Travelers Property Casualty Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>27.500%</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>14.469%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>7425268</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>61714</v>
+        <v>12013</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>51317960</t>
+          <t>4813803</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>70.800%</t>
+          <t>29.143%</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>-5.346%</t>
+          <t>-23.280%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -11403,7 +11255,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>TRVD-133837636</t>
+          <t>SFMA-134657574</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -11413,12 +11265,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133837636/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -11428,12 +11280,12 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
@@ -11446,55 +11298,50 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>02/16/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Travelers Property Casualty Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1.600%</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0.007%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>63226</v>
+        <v>93</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>62314056</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>25.324%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>-25.317%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11504,7 +11351,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>TRVD-134105768</t>
+          <t>SFMA-134657690</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -11514,34 +11361,30 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134105768/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11551,102 +11394,588 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>22159</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>6226337</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0.112%</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-0.019%</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>SFMA-134657690</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>129</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>100484</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>25.385%</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-14.527%</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-0.001%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>3383</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>3157064</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>21.703%</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-19.559%</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>02/23/2024</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>27.500%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>14.469%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>7425268</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>61714</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>51317960</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>70.800%</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-5.346%</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>TRVD-133837636</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/133837636/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>02/16/2025</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1.600%</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0.007%</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>63226</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>62314056</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>25.324%</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-25.317%</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>TRVD-134105768</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134105768/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>09/26/2025</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Travelers Property Casualty Insurance Company</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>21.499%</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>14.416%</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>8787343</t>
         </is>
       </c>
-      <c r="I110" t="n">
+      <c r="I115" t="n">
         <v>58932</v>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>60957168</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>27.673%</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>-11.978%</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t>TRVD-G134570380</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>2025-07-03</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>output/pdfs/NV/134594460/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>ambest_validated</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>ambest_cross_checked</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U115"/>
+  <dimension ref="A1:U114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>03/31/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4490,35 +4490,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.013%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.954%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>848778</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>70869</v>
+        <v>2449</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>20336786</t>
+          <t>7100190</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>40.318%</t>
+          <t>44.037%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-32.351%</t>
+          <t>-0.661%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4528,22 +4528,22 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GECC-134012732</t>
+          <t>GECC-134376338</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Approved with Stipulations</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2024-03-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134012732/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>14.013%</t>
+          <t>40.673%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11.954%</t>
+          <t>17.274%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>848778</t>
+          <t>4264933</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2449</v>
+        <v>11746</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>7100190</t>
+          <t>24689228</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>44.037%</t>
+          <t>51.634%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.661%</t>
+          <t>-2.432%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4697,30 +4697,30 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17.274%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4264933</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11746</v>
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>24689228</t>
+          <t>9112247</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>51.634%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-2.432%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>03/31/2025</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4793,35 +4793,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>40.673%</t>
+          <t>41.000%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.575%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7746706</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>22451</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9112247</t>
+          <t>73251862</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>52.330%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.584%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GECC-134376338</t>
+          <t>GECC-134604501</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4894,35 +4894,35 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>41.000%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10.575%</t>
+          <t>6.431%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7746706</t>
+          <t>12099296</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>22451</v>
+        <v>47423</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>73251862</t>
+          <t>188142494</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>52.330%</t>
+          <t>41.520%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-15.584%</t>
+          <t>-16.865%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4995,35 +4995,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6.431%</t>
+          <t>1.019%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>12099296</t>
+          <t>668230</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>47423</v>
+        <v>15791</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>188142494</t>
+          <t>65553924</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>41.520%</t>
+          <t>32.408%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-16.865%</t>
+          <t>-16.925%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5096,60 +5096,60 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>34.091%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1.019%</t>
+          <t>30.489%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>668230</t>
+          <t>2410417</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>15791</v>
+        <v>2351</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>65553924</t>
+          <t>7905887</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>32.408%</t>
+          <t>81.915%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-16.925%</t>
+          <t>-11.679%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GECC-134604501</t>
+          <t>GECC-134661852</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5197,35 +5197,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>34.091%</t>
+          <t>74.348%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>30.489%</t>
+          <t>56.469%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2410417</t>
+          <t>16269829</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2351</v>
+        <v>13269</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7905887</t>
+          <t>28812212</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>81.915%</t>
+          <t>135.921%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-11.679%</t>
+          <t>-24.946%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>04/11/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5293,65 +5293,65 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>74.348%</t>
+          <t>28.915%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>56.469%</t>
+          <t>6.035%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>16269829</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>13269</v>
+        <v>184</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>28812212</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>135.921%</t>
+          <t>9.677%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-24.946%</t>
+          <t>3.354%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GECC-134661852</t>
+          <t>LBPM-133813014</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U49" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5404,30 +5404,30 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6.035%</t>
+          <t>12.464%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>2561016</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>184</v>
+        <v>8004</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>9.677%</t>
+          <t>22.044%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3.354%</t>
+          <t>0.997%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/11/2024</t>
+          <t>03/18/2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5500,60 +5500,60 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>28.915%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12.464%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2561016</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8004</v>
+        <v>184</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22.044%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.997%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>LBPM-133813014</t>
+          <t>LBPM-133917124</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133813014/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5615,11 +5615,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>184</v>
+        <v>8004</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/18/2024</t>
+          <t>05/20/2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5716,11 +5716,11 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8004</v>
+        <v>184</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>505145</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5735,27 +5735,27 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LBPM-133917124</t>
+          <t>LBPM-133917345</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917124/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5817,11 +5817,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>184</v>
+        <v>8004</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>505145</t>
+          <t>20547982</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>05/20/2024</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5904,35 +5904,35 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.109%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.109%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8004</v>
+        <v>97</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20547982</t>
+          <t>275931</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>86.140%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-26.742%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LBPM-133917345</t>
+          <t>LBPM-133959002</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-01-24</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133917345/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6005,35 +6005,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>8.109%</t>
+          <t>-0.093%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8.109%</t>
+          <t>-0.093%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>-22376</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>97</v>
+        <v>7911</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>275931</t>
+          <t>23950642</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>86.140%</t>
+          <t>202.705%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-26.742%</t>
+          <t>-44.485%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6086,55 +6086,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>07/02/2024</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-0.093%</t>
+          <t>44.500%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-0.093%</t>
+          <t>25.010%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-22376</t>
+          <t>700756</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7911</v>
+        <v>23600</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>23950642</t>
+          <t>2801932</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>202.705%</t>
+          <t>29.690%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-44.485%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>LBPM-133959002</t>
+          <t>LBPM-134070855</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133959002/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -6212,30 +6212,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25.010%</t>
+          <t>26.230%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>700756</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>23600</v>
+        <v>21</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2801932</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>29.690%</t>
+          <t>28.320%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.410%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>07/02/2024</t>
+          <t>02/23/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6303,40 +6303,40 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>44.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>26.230%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>290107</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>28.320%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>16.410%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>LBPM-134070855</t>
+          <t>LBPM-134721941</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134070855/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134721941/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>02/23/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6399,70 +6399,70 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.800%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61748</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>290107</t>
+          <t>552597</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>LBPM-134721941</t>
+          <t>LBPM-134825266</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134721941/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6515,30 +6515,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>3151047</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>165</v>
+        <v>10266</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>552597</t>
+          <t>31426248</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>05/17/2024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6606,65 +6606,65 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>21.800%</t>
+          <t>20.800%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>8.464%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3151047</t>
+          <t>809365</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10266</v>
+        <v>20514</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>31426248</t>
+          <t>9562952</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>42.967%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-7.911%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>LBPM-134825266</t>
+          <t>PRGS-133796059</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6717,30 +6717,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>8.464%</t>
+          <t>7.720%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>809365</t>
+          <t>404153</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>20514</v>
+        <v>11559</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>9562952</t>
+          <t>5235063</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>42.967%</t>
+          <t>48.534%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-7.911%</t>
+          <t>-8.216%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>05/17/2024</t>
+          <t>06/14/2024</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6808,40 +6808,40 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>20.800%</t>
+          <t>9.657%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7.720%</t>
+          <t>2.767%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>404153</t>
+          <t>5190745</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11559</v>
+        <v>131147</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>5235063</t>
+          <t>187628409</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>48.534%</t>
+          <t>28.839%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-8.216%</t>
+          <t>-14.718%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>PRGS-133796059</t>
+          <t>PRGS-133908022</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133796059/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6914,35 +6914,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>9.657%</t>
+          <t>15.044%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.767%</t>
+          <t>4.857%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5190745</t>
+          <t>6334810</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>131147</v>
+        <v>77006</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>187628409</t>
+          <t>130426345</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>28.839%</t>
+          <t>35.330%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-14.718%</t>
+          <t>-19.014%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>06/14/2024</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7015,60 +7015,60 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>15.044%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.857%</t>
+          <t>-0.094%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6334810</t>
+          <t>-311663</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>77006</v>
+        <v>212801</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>130426345</t>
+          <t>331679622</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>35.330%</t>
+          <t>139.114%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-19.014%</t>
+          <t>-58.224%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>PRGS-133908022</t>
+          <t>PRGS-134206539</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133908022/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7121,30 +7121,30 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-0.094%</t>
+          <t>-0.034%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-311663</t>
+          <t>-48815</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>212801</v>
+        <v>84134</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>331679622</t>
+          <t>144277657</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>139.114%</t>
+          <t>151.139%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-58.224%</t>
+          <t>-54.884%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>01/24/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7217,60 +7217,60 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.078%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-0.034%</t>
+          <t>4.976%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-48815</t>
+          <t>12436677</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>84134</v>
+        <v>178171</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>144277657</t>
+          <t>249949453</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>151.139%</t>
+          <t>20.960%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-54.884%</t>
+          <t>-8.513%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PRGS-134206539</t>
+          <t>PRGS-134304882</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7318,35 +7318,35 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>10.078%</t>
+          <t>4.514%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4.976%</t>
+          <t>4.415%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>12436677</t>
+          <t>5696155</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>178171</v>
+        <v>73976</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>249949453</t>
+          <t>129010874</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>20.960%</t>
+          <t>17.679%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-8.513%</t>
+          <t>-4.703%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01/24/2025</t>
+          <t>10/03/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -7419,35 +7419,35 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>4.514%</t>
+          <t>8.410%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4.415%</t>
+          <t>6.865%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>5696155</t>
+          <t>23229304</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>73976</v>
+        <v>212801</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>129010874</t>
+          <t>338370673</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>17.679%</t>
+          <t>15.444%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-4.703%</t>
+          <t>-5.214%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>PRGS-134304882</t>
+          <t>PRGS-134617486</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7520,35 +7520,35 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>8.410%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6.865%</t>
+          <t>-0.003%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>23229304</t>
+          <t>-4282</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>212801</v>
+        <v>84134</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>338370673</t>
+          <t>145129258</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>15.444%</t>
+          <t>22.222%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-5.214%</t>
+          <t>-12.417%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>10/03/2025</t>
+          <t>11/21/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7616,40 +7616,40 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-0.003%</t>
+          <t>12.637%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-4282</t>
+          <t>1529646</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>84134</v>
+        <v>24758</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>145129258</t>
+          <t>12104575</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>22.222%</t>
+          <t>35.507%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-12.417%</t>
+          <t>-4.255%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>PRGS-134617486</t>
+          <t>PRGS-134618970</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -7727,30 +7727,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>12.637%</t>
+          <t>11.765%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1529646</t>
+          <t>721225</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>24758</v>
+        <v>12489</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>12104575</t>
+          <t>6130291</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>35.507%</t>
+          <t>35.429%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-4.255%</t>
+          <t>-3.540%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -7803,80 +7803,80 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>11/21/2025</t>
+          <t>06/27/2024</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>17.600%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>11.765%</t>
+          <t>15.963%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>721225</t>
+          <t>1591348</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>12489</v>
+        <v>7054</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6130291</t>
+          <t>9968913</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>35.429%</t>
+          <t>108.729%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-3.540%</t>
+          <t>-47.427%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>PRGS-134618970</t>
+          <t>LBPM-134016380</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134016380/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>06/27/2024</t>
+          <t>10/02/2024</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7919,65 +7919,65 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>17.600%</t>
+          <t>32.700%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>15.963%</t>
+          <t>7.136%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1591348</t>
+          <t>91374</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7054</v>
+        <v>1570</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9968913</t>
+          <t>1280535</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>108.729%</t>
+          <t>108.945%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-47.427%</t>
+          <t>-13.265%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>LBPM-134016380</t>
+          <t>LBPM-134016692</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134016380/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134016692/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -8005,55 +8005,55 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10/02/2024</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>32.700%</t>
+          <t>15.079%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7.136%</t>
+          <t>9.604%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>91374</t>
+          <t>4089402</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1570</v>
+        <v>11770</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1280535</t>
+          <t>42579372</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>108.945%</t>
+          <t>103.005%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-13.265%</t>
+          <t>-37.335%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>LBPM-134016692</t>
+          <t>LBPM-134446500</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134016692/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
@@ -8106,55 +8106,55 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>10/30/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>15.079%</t>
+          <t>34.200%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>9.604%</t>
+          <t>14.979%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4089402</t>
+          <t>1260251</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>11770</v>
+        <v>5203</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>42579372</t>
+          <t>8413197</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>103.005%</t>
+          <t>90.241%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-37.335%</t>
+          <t>-38.215%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>LBPM-134446500</t>
+          <t>LBPM-134587304</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8207,80 +8207,80 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10/30/2025</t>
+          <t>05/16/2026</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>34.200%</t>
+          <t>12.700%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14.979%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1260251</t>
+          <t>2088534</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5203</v>
+        <v>8943</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>8413197</t>
+          <t>34815867</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>90.241%</t>
+          <t>15.389%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-38.215%</t>
+          <t>-3.608%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>LBPM-134587304</t>
+          <t>LBPM-134798717</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134798717/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8308,80 +8308,80 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>08/15/2024</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>12.700%</t>
+          <t>-7.429%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>-0.002%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2088534</t>
+          <t>-444</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8943</v>
+        <v>42178</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>34815867</t>
+          <t>25637633</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>15.389%</t>
+          <t>21.016%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-3.608%</t>
+          <t>-18.946%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>LBPM-134798717</t>
+          <t>SFMA-133718498</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134798717/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133718498/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>08/15/2024</t>
+          <t>02/15/2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8419,45 +8419,45 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-7.429%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-0.002%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-444</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>42178</v>
+        <v>12973</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>25637633</t>
+          <t>26934045</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>21.016%</t>
+          <t>23.298%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-18.946%</t>
+          <t>-19.292%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-133718498</t>
+          <t>SFMA-133804248</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133718498/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8544,21 +8544,21 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>12973</v>
+        <v>457151</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>26934045</t>
+          <t>509230586</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>23.298%</t>
+          <t>29.298%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-19.292%</t>
+          <t>-29.626%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8611,55 +8611,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>02/15/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.037%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-877</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>457151</v>
+        <v>3459</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>509230586</t>
+          <t>2390223</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>29.298%</t>
+          <t>12.982%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-29.626%</t>
+          <t>-4.962%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8669,7 +8664,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>SFMA-133804248</t>
+          <t>SFMA-133834795</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8679,12 +8674,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-09-29</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133804248/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133834795/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8712,7 +8707,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>05/06/2024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8722,40 +8717,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-0.037%</t>
+          <t>6.256%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-877</t>
+          <t>2031260</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3459</v>
+        <v>13731</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2390223</t>
+          <t>32467635</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>12.982%</t>
+          <t>25.093%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-4.962%</t>
+          <t>-0.135%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-133834795</t>
+          <t>SFMA-133866614</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2023-09-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133834795/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8828,35 +8828,35 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>21.943%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6.256%</t>
+          <t>16.114%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2031260</t>
+          <t>107538939</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>13731</v>
+        <v>472743</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>32467635</t>
+          <t>667363585</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>25.093%</t>
+          <t>26.465%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-0.135%</t>
+          <t>-0.149%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8924,40 +8924,35 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>21.943%</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>16.114%</t>
+          <t>0.019%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>107538939</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>472743</v>
+        <v>993</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>667363585</t>
+          <t>587917</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>26.465%</t>
+          <t>0.081%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-0.149%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8967,7 +8962,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-133866614</t>
+          <t>SFMA-133866656</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8982,7 +8977,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866614/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -9015,7 +9010,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9030,25 +9025,25 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.019%</t>
+          <t>0.026%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>993</v>
+        <v>12453</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>587917</t>
+          <t>4693200</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>0.081%</t>
+          <t>0.088%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9111,7 +9106,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -9121,30 +9116,30 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.026%</t>
+          <t>0.013%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>12453</v>
+        <v>90</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4693200</t>
+          <t>7945</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0.088%</t>
+          <t>0.056%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9159,7 +9154,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>SFMA-133866656</t>
+          <t>SFMA-133866769</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -9174,7 +9169,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866656/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -9207,7 +9202,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -9222,30 +9217,30 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.013%</t>
+          <t>-0.002%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-88</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>90</v>
+        <v>23353</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>5303794</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0.056%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.044%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9298,40 +9293,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>05/06/2024</t>
+          <t>03/21/2024</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-0.002%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>23353</v>
+        <v>213904</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>5303794</t>
+          <t>135349235</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9341,7 +9336,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-0.044%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9351,7 +9346,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>SFMA-133866769</t>
+          <t>SFMA-133905060</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9361,12 +9356,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133866769/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133905060/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -9394,7 +9389,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>03/21/2024</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9412,32 +9407,37 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>14.275%</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.943%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13494733</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>213904</v>
+        <v>214157</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>135349235</t>
+          <t>135725334</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>44.648%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-44.541%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>SFMA-133905060</t>
+          <t>SFMA-133937492</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133905060/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133937492/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U90" t="inlineStr"/>
@@ -9490,7 +9490,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>02/13/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9500,45 +9500,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>14.275%</t>
+          <t>12.565%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>9.943%</t>
+          <t>0.239%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>13494733</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>214157</v>
+        <v>988</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>135725334</t>
+          <t>620002</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>44.648%</t>
+          <t>10.539%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-44.541%</t>
+          <t>-8.078%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>SFMA-133937492</t>
+          <t>SFMA-134076824</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133937492/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9616,30 +9616,30 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.239%</t>
+          <t>0.053%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>988</v>
+        <v>12302</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>620002</t>
+          <t>4752472</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>10.539%</t>
+          <t>10.905%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-8.078%</t>
+          <t>-9.657%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>02/13/2025</t>
+          <t>01/30/2025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9707,40 +9707,40 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>12.565%</t>
+          <t>19.515%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.053%</t>
+          <t>5.562%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2131676</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12302</v>
+        <v>14992</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4752472</t>
+          <t>38322893</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>10.905%</t>
+          <t>31.358%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-9.657%</t>
+          <t>-11.312%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>SFMA-134076824</t>
+          <t>SFMA-134207336</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134076824/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9813,35 +9813,35 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>19.515%</t>
+          <t>12.802%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>5.562%</t>
+          <t>8.451%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2131676</t>
+          <t>65333740</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>14992</v>
+        <v>471771</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>38322893</t>
+          <t>773123310</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>31.358%</t>
+          <t>39.658%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-11.312%</t>
+          <t>-10.532%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9909,40 +9909,40 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>12.802%</t>
+          <t>15.860%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>8.451%</t>
+          <t>3.928%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>65333740</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>471771</v>
+        <v>988</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>773123310</t>
+          <t>618865</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>39.658%</t>
+          <t>24.824%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>-10.532%</t>
+          <t>-10.038%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>SFMA-134207336</t>
+          <t>SFMA-134207352</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -10020,30 +10020,30 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>3.928%</t>
+          <t>0.935%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>988</v>
+        <v>12302</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>618865</t>
+          <t>4826799</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>24.824%</t>
+          <t>17.063%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-10.038%</t>
+          <t>-15.535%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -10111,40 +10111,40 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>15.860%</t>
+          <t>33.352%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0.935%</t>
+          <t>9.953%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>12302</v>
+        <v>60</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4826799</t>
+          <t>48460</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>17.063%</t>
+          <t>20.430%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-15.535%</t>
+          <t>-0.321%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>SFMA-134207352</t>
+          <t>SFMA-134207394</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -10222,30 +10222,30 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>9.953%</t>
+          <t>9.987%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>275821</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>60</v>
+        <v>3997</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>48460</t>
+          <t>2761789</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>20.430%</t>
+          <t>24.641%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-0.321%</t>
+          <t>-3.157%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -10318,35 +10318,35 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>33.352%</t>
+          <t>44.880%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>9.987%</t>
+          <t>15.049%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>275821</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3997</v>
+        <v>89</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2761789</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>24.641%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-3.157%</t>
+          <t>7.963%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>SFMA-134207394</t>
+          <t>SFMA-134207400</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -10424,30 +10424,30 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>15.049%</t>
+          <t>10.492%</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>569929</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>89</v>
+        <v>23890</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>5432068</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>50.000%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>7.963%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10500,12 +10500,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01/30/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -10515,40 +10515,40 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>44.880%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>10.492%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>569929</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>23890</v>
+        <v>19632</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>5432068</t>
+          <t>32973867</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>50.000%</t>
+          <t>22.218%</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-29.296%</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10558,7 +10558,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>SFMA-134207400</t>
+          <t>SFMA-134293428</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -10635,21 +10635,21 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>19632</v>
+        <v>461410</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>32973867</t>
+          <t>574804392</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>22.218%</t>
+          <t>31.288%</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>-29.296%</t>
+          <t>-29.283%</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10702,55 +10702,55 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>11/15/2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>29.236%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.908%</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1227629</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>461410</v>
+        <v>10157</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>574804392</t>
+          <t>4928614</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>31.288%</t>
+          <t>29.493%</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>-29.283%</t>
+          <t>15.948%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>SFMA-134293428</t>
+          <t>SFMA-134400219</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>11/15/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -10813,45 +10813,45 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>29.236%</t>
+          <t>21.094%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>24.908%</t>
+          <t>2.861%</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1227629</t>
+          <t>987176</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>10157</v>
+        <v>20202</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4928614</t>
+          <t>34509460</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>29.493%</t>
+          <t>387.674%</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>15.948%</t>
+          <t>-85.971%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>SFMA-134400219</t>
+          <t>SFMA-134576755</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -10924,35 +10924,35 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>21.094%</t>
+          <t>8.538%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2.861%</t>
+          <t>2.694%</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>987176</t>
+          <t>22650482</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>20202</v>
+        <v>464314</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>34509460</t>
+          <t>840691111</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>387.674%</t>
+          <t>521.639%</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>-85.971%</t>
+          <t>-93.331%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -11020,40 +11020,35 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>8.538%</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2.694%</t>
+          <t>-0.001%</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>22650482</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>464314</v>
+        <v>1098</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>840691111</t>
+          <t>650459</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>521.639%</t>
+          <t>27.169%</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>-93.331%</t>
+          <t>-22.150%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -11063,7 +11058,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>SFMA-134576755</t>
+          <t>SFMA-134657574</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -11073,12 +11068,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -11111,7 +11106,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -11126,7 +11121,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-0.001%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11135,21 +11130,21 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1098</v>
+        <v>12013</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>650459</t>
+          <t>4813803</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>27.169%</t>
+          <t>29.143%</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>-22.150%</t>
+          <t>-23.280%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11207,7 +11202,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -11217,7 +11212,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -11227,25 +11222,25 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>12013</v>
+        <v>93</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>4813803</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>29.143%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>-23.280%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -11255,7 +11250,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>SFMA-134657574</t>
+          <t>SFMA-134657690</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -11265,12 +11260,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -11303,7 +11298,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -11323,25 +11318,25 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>93</v>
+        <v>22159</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>6226337</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.112%</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.019%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11399,7 +11394,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -11419,25 +11414,25 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>22159</v>
+        <v>129</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>6226337</t>
+          <t>100484</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>0.112%</t>
+          <t>25.385%</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>-0.019%</t>
+          <t>-14.527%</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -11447,7 +11442,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>SFMA-134657690</t>
+          <t>SFMA-134657829</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -11457,12 +11452,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -11495,7 +11490,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -11510,30 +11505,30 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.001%</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-35</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>129</v>
+        <v>3383</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>100484</t>
+          <t>3157064</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>25.385%</t>
+          <t>21.703%</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>-14.527%</t>
+          <t>-19.559%</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -11586,50 +11581,55 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>02/23/2024</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Property Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>27.500%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-0.001%</t>
+          <t>14.469%</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-35</t>
+          <t>7425268</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3383</v>
+        <v>61714</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>3157064</t>
+          <t>51317960</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>21.703%</t>
+          <t>70.800%</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>-19.559%</t>
+          <t>-5.346%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>SFMA-134657829</t>
+          <t>TRVD-133837636</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+          <t>output/pdfs/NV/133837636/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U112" t="inlineStr"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>02/23/2024</t>
+          <t>02/16/2025</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -11702,35 +11702,35 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>27.500%</t>
+          <t>1.600%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>14.469%</t>
+          <t>0.007%</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>7425268</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>61714</v>
+        <v>63226</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>51317960</t>
+          <t>62314056</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>70.800%</t>
+          <t>25.324%</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>-5.346%</t>
+          <t>-25.317%</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>TRVD-133837636</t>
+          <t>TRVD-134105768</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -11750,12 +11750,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/133837636/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134105768/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U113" t="inlineStr"/>
@@ -11783,7 +11783,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>02/16/2025</t>
+          <t>09/26/2025</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11803,35 +11803,35 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.600%</t>
+          <t>21.499%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>0.007%</t>
+          <t>14.416%</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>8787343</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>63226</v>
+        <v>58932</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>62314056</t>
+          <t>60957168</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>25.324%</t>
+          <t>27.673%</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>-25.317%</t>
+          <t>-11.978%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>TRVD-134105768</t>
+          <t>TRVD-G134570380</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>output/pdfs/NV/134105768/filing_summary.pdf</t>
+          <t>output/pdfs/NV/134594460/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -11875,107 +11875,6 @@
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>NV</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>09/26/2025</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Travelers Property Casualty Insurance Company</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>21.499%</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>14.416%</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>8787343</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>58932</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>60957168</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>27.673%</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>-11.978%</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>TRVD-G134570380</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>2025-07-03</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>output/pdfs/NV/134594460/filing_summary.pdf</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>pipeline_only</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/nv_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U114"/>
+  <dimension ref="A1:U159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11875,6 +11875,4326 @@
         </is>
       </c>
       <c r="U114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>07/15/2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>73.070%</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>9.465%</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>17354170</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>226125</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>183361599</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>84.400%</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-47.154%</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>SFMA-134939403</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134939403/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>7.841%</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>5.853%</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>20492321</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>237181</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>350143433</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>23.944%</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-15.136%</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>PRGS-135014276</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/135014276/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>11/13/2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2.770%</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2.860%</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>4563842</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>94393</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>159581312</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>12.271%</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-15.686%</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>PRGS-135014276</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/135014276/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>26.475%</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>7.971%</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>23745054</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>55814</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>297893706</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>41.104%</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-14.352%</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ALSE-134923648</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134923648/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>33.162%</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>6.706%</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>424717</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1015</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>6333778</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>18.260%</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-4.802%</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ALSE-134923710</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134923710/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1.090%</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-9.221%</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-59343</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>309</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>643587</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>250.800%</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-36.550%</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>LBPM-134938186</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134938186/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>692</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>1426291</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>LBPM-135029660</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/135029660/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10/30/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>14.704%</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>11.977%</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>199124</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>2277</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>1662597</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>12.100%</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>3.388%</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>LBPM-135023203</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/135023203/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Farmers Group Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>22.400%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>8.712%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1710573</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>4979</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>19633852</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>44.300%</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-32.800%</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>FAIG-134898606</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134898606/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>27.900%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>8.087%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>846608</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>2583</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>10468749</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>222.100%</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-24.800%</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>FAIG-134896844</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134896844/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>15.162%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>11.271%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>8835685</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>19968</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>78393469</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>31.624%</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-7.971%</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>AMFC-134975924</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134975924/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0.001%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>5059</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>18262376</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>2.057%</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>CFPC-134931698</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931698/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>9148</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>30852282</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0.421%</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>CFPC-134931698</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931698/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>360</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>1296092</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>CFPC-134931698</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931698/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>25.630%</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-0.786%</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-111863</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>4156</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>14223192</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>-22.600%</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>CFPC-134899062</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>25.632%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-0.395%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-122303</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>9524</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>30991489</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>-22.800%</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>CFPC-134899062</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>23.313%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-3.523%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-51169</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>388</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>1452544</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-23.500%</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>CFPC-134899062</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>19.218%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>3509653</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>5059</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>18262376</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>70.301%</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-12.701%</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>CFPC-134954773</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954773/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>13.608%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>4198460</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>9148</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>30852282</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>56.419%</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>-20.730%</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>CFPC-134954773</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954773/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>14.015%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>181652</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>360</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>1296092</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>38.613%</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>-12.689%</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>CFPC-134954773</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954773/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>25.630%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-0.112%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-156</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>161</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>138766</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-11.100%</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>CFPC-134899246</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899246/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>25.632%</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-0.270%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-816</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>427</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>302501</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-17.800%</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>CFPC-134899246</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899246/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>23.313%</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>11</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>8904</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>CFPC-134899246</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899246/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2.214%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>211</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>170655</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>42.863%</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-26.747%</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>CFPC-134954860</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954860/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-1.739%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-5158</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>420</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>296608</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>34.489%</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-31.477%</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>CFPC-134954860</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954860/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-0.278%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-36</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>13</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>13038</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>9.209%</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-9.344%</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>CFPC-134954860</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954860/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>243</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>137365</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-0.081%</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>CFPC-134931722</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>541</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>298227</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-0.010%</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>CFPC-134931722</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>08/24/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>9</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>11400</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>CFPC-134931722</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134931722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>5.717%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>7854</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>243</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>137365</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>22.080%</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>0.521%</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>CFPC-134954895</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954895/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>5.969%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>17802</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>541</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>298227</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>37.794%</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-1.175%</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>CFPC-134954895</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954895/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>6.506%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>742</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>9</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>11400</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>13.384%</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>3.654%</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>CFPC-134954895</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954895/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>25.630%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0.005%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>164</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>103810</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0.631%</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>CFPC-134899770</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899770/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>25.632%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0.003%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>422</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>254810</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0.997%</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>CFPC-134899770</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899770/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>23.313%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>7331</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>CFPC-134899770</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134899770/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>29.066%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0.495%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>990</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>654939</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>35.576%</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-19.677%</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>CFPC-134954919</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954919/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>19.039%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-0.668%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-4849</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1598</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>725668</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>27.137%</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-21.742%</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>CFPC-134954919</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954919/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>09/21/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>20.967%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1.471%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>18</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>17378</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>13.987%</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-6.652%</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>CFPC-134954919</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134954919/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>25.630%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-0.022%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-124</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>909</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>570487</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>3.330%</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-9.938%</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>CFPC-134900062</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134900062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>25.632%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-0.117%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-825</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1605</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>703398</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>3.961%</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-11.716%</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>CFPC-134900062</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134900062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>23.313%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-0.820%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-106</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>20</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>12925</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-18.750%</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>CFPC-134900062</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134900062/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>8.500%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>9.475%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>4458198</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>15718</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>47052564</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>38.231%</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>-17.771%</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>USAA-134941475</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134941907/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>8.600%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>10.017%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>7466826</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>24081</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>74543668</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>41.353%</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-26.836%</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>USAA-134941475</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134941907/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>19.600%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20.693%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>19457695</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>32209</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>94032452</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>63.458%</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-14.335%</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>USAA-134941475</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134941907/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>10/03/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>19.200%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20.829%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>19025822</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>27850</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>91343090</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>60.282%</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-13.684%</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>USAA-134941475</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134941907/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
